--- a/output/pdf_financials_xlsx/GIGA.xlsx
+++ b/output/pdf_financials_xlsx/GIGA.xlsx
@@ -1390,13 +1390,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.939923</v>
+        <v>-4.496345</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.102822</v>
+        <v>-4.019356</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.261788</v>
+        <v>-2.693288</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0.197502</v>
@@ -1405,13 +1405,13 @@
         <v>-2.2e-05</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.380398</v>
+        <v>-1.018802</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0.068652</v>
+        <v>-0.65981</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0.2132</v>
+        <v>-45.820226</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-20.461048</v>
@@ -1647,28 +1647,28 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.778211</v>
+        <v>-1.778211</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.958267</v>
+        <v>-1.958267</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.477538</v>
+        <v>-1.477538</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.2201</v>
+        <v>-1.2201</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.630653</v>
+        <v>-1.630653</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.319202</v>
+        <v>-0.319202</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.295579</v>
+        <v>-0.295579</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>22.803513</v>
+        <v>-22.803513</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-10.230524</v>
@@ -1836,28 +1836,28 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.778211</v>
+        <v>-1.778211</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.958267</v>
+        <v>-1.958267</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.477538</v>
+        <v>-1.477538</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.2201</v>
+        <v>-1.2201</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.630653</v>
+        <v>-1.630653</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.319202</v>
+        <v>-0.319202</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.295579</v>
+        <v>-0.295579</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>22.803513</v>
+        <v>-22.803513</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-10.230524</v>
@@ -2025,19 +2025,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-59.2737</v>
+        <v>59.2737</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-65.275567</v>
+        <v>65.275567</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-73.87690000000001</v>
+        <v>73.87690000000001</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-61.005</v>
+        <v>61.005</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-81.53265</v>
+        <v>81.53265</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-18.098026</v>
+        <v>18.098026</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>17.948288</v>
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>34.57971534883858</v>
+        <v>165.4202846511614</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>4.988721981437968</v>
+        <v>195.0112780185621</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>21.53304544519844</v>
+        <v>221.5330454451984</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>13.93211917026077</v>
@@ -2397,13 +2397,13 @@
         <v>0.001349170965104919</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>54.37364208118925</v>
+        <v>145.6263579188108</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>18.84847802630748</v>
+        <v>181.1515219736925</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.9262834358667982</v>
+        <v>199.0737165641332</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>200</v>
@@ -6435,46 +6435,46 @@
         <v>5.183894</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>5.791977</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.035603</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.153639</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>6.153639</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>6.153639</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.19647</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>6.745535</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.255441</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.763393</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>9.567417000000001</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>10.826508</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>11.261049</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>11.428578</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>11.659267</v>
       </c>
     </row>
     <row r="93">
@@ -11178,7 +11178,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -14156,7 +14160,11 @@
           <t>Share-based payment reserve 12</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -18172,7 +18180,11 @@
           <t>Share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -46509,13 +46521,13 @@
         </is>
       </c>
       <c r="J362" s="5" t="n">
-        <v>0.319202</v>
+        <v>-0.319202</v>
       </c>
       <c r="K362" s="5" t="n">
-        <v>0.295579</v>
+        <v>-0.295579</v>
       </c>
       <c r="L362" s="5" t="n">
-        <v>22.803513</v>
+        <v>-22.803513</v>
       </c>
       <c r="M362" s="5" t="n">
         <v>-10.230524</v>
@@ -49033,13 +49045,13 @@
         </is>
       </c>
       <c r="H386" s="5" t="n">
-        <v>1.2201</v>
+        <v>-1.2201</v>
       </c>
       <c r="I386" s="5" t="n">
-        <v>1.630653</v>
+        <v>-1.630653</v>
       </c>
       <c r="J386" s="5" t="n">
-        <v>0.319202</v>
+        <v>-0.319202</v>
       </c>
       <c r="K386" t="inlineStr">
         <is>
@@ -53865,13 +53877,13 @@
         </is>
       </c>
       <c r="F432" s="5" t="n">
-        <v>1.958267</v>
+        <v>-1.958267</v>
       </c>
       <c r="G432" s="5" t="n">
-        <v>1.477538</v>
+        <v>-1.477538</v>
       </c>
       <c r="H432" s="5" t="n">
-        <v>1.21952</v>
+        <v>-1.21952</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
@@ -55522,13 +55534,13 @@
         </is>
       </c>
       <c r="E448" s="5" t="n">
-        <v>1.778211</v>
+        <v>-1.778211</v>
       </c>
       <c r="F448" s="5" t="n">
-        <v>1.958267</v>
+        <v>-1.958267</v>
       </c>
       <c r="G448" s="5" t="n">
-        <v>1.477538</v>
+        <v>-1.477538</v>
       </c>
       <c r="H448" t="inlineStr">
         <is>
@@ -55836,13 +55848,13 @@
         </is>
       </c>
       <c r="E451" s="5" t="n">
-        <v>1.778211</v>
+        <v>-1.778211</v>
       </c>
       <c r="F451" s="5" t="n">
-        <v>1.958267</v>
+        <v>-1.958267</v>
       </c>
       <c r="G451" s="5" t="n">
-        <v>1.477538</v>
+        <v>-1.477538</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GIGA.xlsx
+++ b/output/pdf_financials_xlsx/GIGA.xlsx
@@ -1078,37 +1078,37 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.463052</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022688</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.051175</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.018024</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005856</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005388</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004124</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003576</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001302</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006275</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.03595</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1116,19 +1116,19 @@
         </is>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.016694</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.07038</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.123137</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.021976</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008685</v>
       </c>
     </row>
     <row r="13">
@@ -2099,37 +2099,37 @@
         <v>2.718134</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.061089</v>
+        <v>2.524141</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.21575</v>
+        <v>1.238438</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.417602</v>
+        <v>1.468777</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.630631</v>
+        <v>1.648655</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.6996</v>
+        <v>0.705456</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.364231</v>
+        <v>0.369619</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>23.016713</v>
+        <v>23.020837</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>10.230524</v>
+        <v>10.2341</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.224112</v>
+        <v>-0.22281</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.683299</v>
+        <v>-0.677024</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.150637</v>
+        <v>1.186587</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2137,19 +2137,19 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.738159</v>
+        <v>-2.721465</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.856597</v>
+        <v>-2.786217</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.055189</v>
+        <v>-1.932052</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-3.025029</v>
+        <v>-3.003053</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.813989</v>
+        <v>-0.805304</v>
       </c>
     </row>
     <row r="28">
@@ -2225,37 +2225,37 @@
         <v>2.718134</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.061089</v>
+        <v>2.524141</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.21575</v>
+        <v>1.238438</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.417602</v>
+        <v>1.468777</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.630631</v>
+        <v>1.648655</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.710493</v>
+        <v>0.716349</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.374348</v>
+        <v>0.379736</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>23.021795</v>
+        <v>23.025919</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>10.2344</v>
+        <v>10.237976</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.221144</v>
+        <v>-0.219842</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.683299</v>
+        <v>-0.677024</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.150637</v>
+        <v>1.186587</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2263,19 +2263,19 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.738159</v>
+        <v>-2.721465</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.856597</v>
+        <v>-2.786217</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.941911</v>
+        <v>-1.818774</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.908071</v>
+        <v>-2.886095</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.748035</v>
+        <v>-0.73935</v>
       </c>
     </row>
     <row r="30">
@@ -2565,19 +2565,19 @@
         <v>0.813736</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.23653</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.518489</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.09965499999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.09589300000000001</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.011964</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.085758</v>
@@ -2695,19 +2695,19 @@
         <v>0.813736</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.23653</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.518489</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.09965499999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.09589300000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.011964</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.085758</v>
@@ -3475,19 +3475,19 @@
         <v>0.060126</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.264155</v>
+        <v>0.027625</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.536471</v>
+        <v>0.017982</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.115585</v>
+        <v>0.01593</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.107499</v>
+        <v>0.011606</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.01856</v>
+        <v>0.006596</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.008406</v>
@@ -9730,7 +9730,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -17372,7 +17376,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -17872,7 +17876,11 @@
           <t>Reclamation deposits 14</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -18928,7 +18936,11 @@
           <t>Reclamation deposits 337,900 187,900</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -26916,7 +26928,11 @@
           <t>Increase in reclamation deposits</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -27650,7 +27666,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -29098,7 +29118,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -38686,7 +38710,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -46292,7 +46316,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -47644,7 +47668,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -48706,7 +48730,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -53554,7 +53578,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">

--- a/output/pdf_financials_xlsx/GIGA.xlsx
+++ b/output/pdf_financials_xlsx/GIGA.xlsx
@@ -766,16 +766,16 @@
         <v>1.131725</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.710543</v>
+        <v>0.7345429999999999</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.817499</v>
+        <v>0.841499</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.8611</v>
+        <v>0.8851</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.601631</v>
+        <v>0.605631</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.239606</v>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.182058</v>
+        <v>1.440897</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.915701</v>
+        <v>1.1799</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.770799</v>
+        <v>1.180441</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.649981</v>
+        <v>1.053726</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.671485</v>
+        <v>0.976955</v>
       </c>
     </row>
     <row r="8">
@@ -955,7 +955,7 @@
         <v>1.42553</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.772736</v>
+        <v>0.796736</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>1.464046</v>
@@ -1380,7 +1380,7 @@
         <v>-3.025029</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-0.813989</v>
+        <v>-0.113989</v>
       </c>
     </row>
     <row r="17">
@@ -1405,13 +1405,13 @@
         <v>-2.2e-05</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-1.018802</v>
+        <v>0.380398</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0.65981</v>
+        <v>0.068652</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-45.820226</v>
+        <v>0.2132</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-20.461048</v>
@@ -1443,7 +1443,7 @@
         <v>0.7</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="18">
@@ -2149,7 +2149,7 @@
         <v>-3.003053</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.805304</v>
+        <v>-0.105304</v>
       </c>
     </row>
     <row r="28">
@@ -2275,7 +2275,7 @@
         <v>-2.886095</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.73935</v>
+        <v>-0.03935</v>
       </c>
     </row>
     <row r="30">
@@ -2397,13 +2397,13 @@
         <v>0.001349170965104919</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>145.6263579188108</v>
+        <v>54.37364208118925</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>181.1515219736925</v>
+        <v>18.84847802630748</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>199.0737165641332</v>
+        <v>0.9262834358667982</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>200</v>
@@ -2435,7 +2435,7 @@
         <v>-23.14027402712503</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0</v>
+        <v>-614.0943424365508</v>
       </c>
     </row>
     <row r="32">
@@ -4566,31 +4566,31 @@
         <v>0</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.00497</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.134982</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.229422</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.235421</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.278244</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.432353</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.127527</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>0.079071</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>0</v>
+        <v>0.192355</v>
       </c>
     </row>
     <row r="65">
@@ -4826,31 +4826,31 @@
         <v>0.015849</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.01497</v>
+        <v>0.01994</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.144982</v>
+        <v>0.279964</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0.312981</v>
+        <v>0.542403</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.383785</v>
+        <v>0.619206</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.341225</v>
+        <v>0.619469</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0.613221</v>
+        <v>1.045574</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0.286136</v>
+        <v>0.413663</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>0.179836</v>
+        <v>0.258907</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>0.398428</v>
+        <v>0.5907829999999999</v>
       </c>
     </row>
     <row r="69">
@@ -5290,22 +5290,22 @@
         <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.07607</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.101707</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.092347</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.109408</v>
+        <v>0</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>0.030073</v>
+        <v>0</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>0.202044</v>
+        <v>0.009689</v>
       </c>
     </row>
     <row r="76">
@@ -7552,16 +7552,16 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.029585</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.03909</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.010218</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004001</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -7582,28 +7582,28 @@
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000856</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.072364</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003594</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.038084</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004151</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.7270180000000001</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000392</v>
       </c>
       <c r="S111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004507</v>
       </c>
     </row>
     <row r="112">
@@ -9073,16 +9073,16 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.029585</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.03909</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.010218</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004001</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -9103,28 +9103,28 @@
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000856</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.072364</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003594</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.038084</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004151</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.7270180000000001</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000392</v>
       </c>
       <c r="S134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004507</v>
       </c>
     </row>
     <row r="135">
@@ -9134,10 +9134,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>0</v>
+        <v>-0.029585</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>0</v>
+        <v>-0.03909</v>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.181496</v>
+        <v>-1.185497</v>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
@@ -9168,28 +9168,28 @@
         <v>-0.142497</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.512283</v>
+        <v>-0.513139</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-1.344283</v>
+        <v>-1.416647</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-1.390827</v>
+        <v>-1.394421</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-1.826065</v>
+        <v>-1.864149</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-1.558331</v>
+        <v>-1.562482</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-1.45326</v>
+        <v>-2.180278</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-1.419957</v>
+        <v>-1.420349</v>
       </c>
       <c r="S135" s="3" t="n">
-        <v>-0.907366</v>
+        <v>-0.911873</v>
       </c>
     </row>
   </sheetData>
@@ -24212,7 +24212,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -25986,7 +25990,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -29334,7 +29342,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -35150,7 +35162,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E252" s="5" t="n">
         <v>-0.939923</v>
       </c>
@@ -36076,7 +36092,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E261" s="5" t="n">
         <v>-0.029585</v>
       </c>
@@ -36280,7 +36300,11 @@
           <t>Proceeds from share issuances, net</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -38240,7 +38264,11 @@
           <t>Management and directors’ fees 12</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -39502,7 +39530,11 @@
           <t>Deferred income tax recovery (expense) 9</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -40128,7 +40160,11 @@
           <t>Management and directors fees 12</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -46922,7 +46958,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -47456,7 +47496,11 @@
           <t>Director fees 12</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -47776,7 +47820,11 @@
           <t>Deferred income tax (recovery) expense 9</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -48944,7 +48992,11 @@
           <t>Deferred income tax (recovery) expense 9</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -50006,7 +50058,11 @@
           <t>Director fees 10</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -52020,7 +52076,11 @@
           <t>Director fees (Note 5)</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -54512,7 +54572,11 @@
           <t>Director fees (Note 6)</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E438" t="inlineStr">
         <is>
           <t>-</t>
